--- a/Assets/Scripts/Csv/00_UnitCard.xlsx
+++ b/Assets/Scripts/Csv/00_UnitCard.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity_Projects\FantasyOffense\Assets\Scripts\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B063E267-D35F-4E7F-A687-C584EE5DB01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D286E908-7487-498A-B1F4-4F856309DB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B898308D-384D-4798-8FE8-60478F2FF85F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B898308D-384D-4798-8FE8-60478F2FF85F}"/>
   </bookViews>
   <sheets>
     <sheet name="00_UnitCard" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
   <si>
     <t>Card_ID</t>
   </si>
@@ -174,21 +174,9 @@
     <t>Value</t>
   </si>
   <si>
-    <t>WORD_DESC_STRONG</t>
-  </si>
-  <si>
-    <t>WORD_NAME_STRONG</t>
-  </si>
-  <si>
     <t>Strong</t>
   </si>
   <si>
-    <t>WORD_DESC_CLONE</t>
-  </si>
-  <si>
-    <t>WORD_NAME_CLONE</t>
-  </si>
-  <si>
     <t>Clone</t>
   </si>
   <si>
@@ -217,12 +205,6 @@
   </si>
   <si>
     <t>// [Enemy]</t>
-  </si>
-  <si>
-    <t>강력한</t>
-  </si>
-  <si>
-    <t>복제된</t>
   </si>
   <si>
     <t>// [Word]</t>
@@ -268,55 +250,55 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Quick</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fast</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Healthy</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>건강한</t>
+    <t>Ignite</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>빠른</t>
+    <t>Cold</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>성급한</t>
+    <t>WORD_NAME_IGNITE</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_NAME_HEALTHY</t>
+    <t>WORD_NAME_EXTRAHIT</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_DESC_STRONG</t>
+    <t>ExtraHit</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_DESC_HEALTHY</t>
+    <t>WORD_NAME_COLD</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_NAME_FAST</t>
+    <t>WORD_DESC_IGNITE</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_DESC_FAST</t>
+    <t>WORD_DESC_EXTRAHIT</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_NAME_QUICK</t>
+    <t>WORD_DESC_COLD</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>WORD_DESC_QUICK</t>
+    <t>발화</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가타</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1374,7 +1356,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
@@ -1617,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F91D85C1-6DD7-4622-9255-8ED269DDA1AB}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.75" customWidth="1"/>
@@ -1640,72 +1622,44 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
         <v>76</v>
       </c>
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1741,7 +1695,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -1885,18 +1839,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1906,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -1922,7 +1876,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -1938,7 +1892,7 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -1954,7 +1908,7 @@
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -1967,7 +1921,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1977,7 +1931,7 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>43</v>
@@ -1993,7 +1947,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
         <v>40</v>
@@ -2009,7 +1963,7 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
@@ -2022,96 +1976,69 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" t="s">
         <v>82</v>
       </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B27"/>
       <c r="C27"/>
     </row>
     <row r="28" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>88</v>
-      </c>
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2121,10 +2048,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2137,10 +2064,10 @@
         <v>30</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -2153,10 +2080,10 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2169,10 +2096,10 @@
         <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Csv/00_UnitCard.xlsx
+++ b/Assets/Scripts/Csv/00_UnitCard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Unity_Projects\FantasyOffense\Assets\Scripts\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D286E908-7487-498A-B1F4-4F856309DB09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C1E22-04AA-4864-B18F-549E4E40A934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B898308D-384D-4798-8FE8-60478F2FF85F}"/>
+    <workbookView xWindow="5055" yWindow="2415" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{B898308D-384D-4798-8FE8-60478F2FF85F}"/>
   </bookViews>
   <sheets>
     <sheet name="00_UnitCard" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="87">
   <si>
     <t>Card_ID</t>
   </si>
@@ -299,6 +299,22 @@
   </si>
   <si>
     <t>냉기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fireball</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPELL_NAME_FIREBALL</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPELL_DESC_FIREBALL</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1504,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B58A9B6-4F5A-449F-985A-B884B4200EF3}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.5" customWidth="1"/>
@@ -1589,6 +1605,26 @@
       </c>
       <c r="F4" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +1867,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71425F1B-0AD5-4E4B-8C49-D3602833EA0C}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.375" customWidth="1"/>
@@ -1974,136 +2010,152 @@
         <v>35</v>
       </c>
     </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+    </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>77</v>
-      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>76</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>79</v>
       </c>
-      <c r="B27"/>
-      <c r="C27"/>
-    </row>
-    <row r="28" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28"/>
-      <c r="B28"/>
-      <c r="C28"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B29"/>
+      <c r="C29"/>
+    </row>
+    <row r="30" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>23</v>
       </c>
     </row>
